--- a/src/assets/employees/rafik.xlsx
+++ b/src/assets/employees/rafik.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F26"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -739,9 +739,189 @@
         <v>2026-09-10</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>rafik</v>
+      </c>
+      <c r="B18" t="str">
+        <v>dev automatisme</v>
+      </c>
+      <c r="C18" t="str">
+        <v>additive clc_clsb</v>
+      </c>
+      <c r="D18" t="str">
+        <v>etude et modifie signaux de comm pasto CLC Additif</v>
+      </c>
+      <c r="E18">
+        <v>4</v>
+      </c>
+      <c r="F18" t="str">
+        <v>2026-09-11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>rafik</v>
+      </c>
+      <c r="B19" t="str">
+        <v>dev automatisme</v>
+      </c>
+      <c r="C19" t="str">
+        <v>habibo madagascar</v>
+      </c>
+      <c r="D19" t="str">
+        <v>modif programme stork madagascar</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19" t="str">
+        <v>2026-09-11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>rafik</v>
+      </c>
+      <c r="B20" t="str">
+        <v>dev automatisme</v>
+      </c>
+      <c r="C20" t="str">
+        <v>habibo madagascar</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Simulation programme STORK madagascar</v>
+      </c>
+      <c r="E20">
+        <v>5</v>
+      </c>
+      <c r="F20" t="str">
+        <v>2026-09-14</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>rafik</v>
+      </c>
+      <c r="B21" t="str">
+        <v>dev automatisme</v>
+      </c>
+      <c r="C21" t="str">
+        <v>intervention SAV</v>
+      </c>
+      <c r="D21" t="str">
+        <v>simulation programme natilait et régulation machine nova 2</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21" t="str">
+        <v>2026-09-14</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>rafik</v>
+      </c>
+      <c r="B22" t="str">
+        <v>dev automatisme</v>
+      </c>
+      <c r="C22" t="str">
+        <v>intervention SAV</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Déplacement Natilait</v>
+      </c>
+      <c r="E22">
+        <v>12</v>
+      </c>
+      <c r="F22" t="str">
+        <v>2026-09-15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>rafik</v>
+      </c>
+      <c r="B23" t="str">
+        <v>dev automatisme</v>
+      </c>
+      <c r="C23" t="str">
+        <v>sonede</v>
+      </c>
+      <c r="D23" t="str">
+        <v>test électrique des armoires sonede</v>
+      </c>
+      <c r="E23">
+        <v>4</v>
+      </c>
+      <c r="F23" t="str">
+        <v>2026-09-16</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>rafik</v>
+      </c>
+      <c r="B24" t="str">
+        <v>dev automatisme</v>
+      </c>
+      <c r="C24" t="str">
+        <v>sonede</v>
+      </c>
+      <c r="D24" t="str">
+        <v>vérification et compréhension redondance logicielle pour sonede</v>
+      </c>
+      <c r="E24">
+        <v>3</v>
+      </c>
+      <c r="F24" t="str">
+        <v>2026-09-16</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>rafik</v>
+      </c>
+      <c r="B25" t="str">
+        <v>dev automatisme</v>
+      </c>
+      <c r="C25" t="str">
+        <v>additive clc_clsb</v>
+      </c>
+      <c r="D25" t="str">
+        <v>deplacement clsb</v>
+      </c>
+      <c r="E25">
+        <v>10</v>
+      </c>
+      <c r="F25" t="str">
+        <v>2026-09-18</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>rafik</v>
+      </c>
+      <c r="B26" t="str">
+        <v>dev automatisme</v>
+      </c>
+      <c r="C26" t="str">
+        <v>sonede</v>
+      </c>
+      <c r="D26" t="str">
+        <v>armoire électrique ( emballage ..)</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+      <c r="F26" t="str">
+        <v>2026-09-18</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F26"/>
   </ignoredErrors>
 </worksheet>
 </file>